--- a/Assets/Originals/Excels/Goal/GoalMessage.xlsx
+++ b/Assets/Originals/Excels/Goal/GoalMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Goal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5209515-8C71-4188-814B-A9435187E7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C5E156-5D4F-4F99-8F76-A19045462CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -161,6 +161,24 @@
   </si>
   <si>
     <t>Este não é o item correto</t>
+  </si>
+  <si>
+    <t>messageRussian</t>
+  </si>
+  <si>
+    <t>messageSizeRussian</t>
+  </si>
+  <si>
+    <t>Соберите Документы</t>
+  </si>
+  <si>
+    <t>Соберите Загадочные предметы</t>
+  </si>
+  <si>
+    <t>Выберите предмет, связанный с Документом</t>
+  </si>
+  <si>
+    <t>Это не тот предмет</t>
   </si>
 </sst>
 </file>
@@ -215,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -228,7 +246,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -509,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="45.375" style="1" customWidth="1"/>
@@ -524,9 +541,11 @@
     <col min="11" max="11" width="20.75" customWidth="1"/>
     <col min="12" max="12" width="41.25" customWidth="1"/>
     <col min="13" max="13" width="23.625" customWidth="1"/>
+    <col min="14" max="14" width="76.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -560,21 +579,25 @@
       <c r="K1" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -608,14 +631,20 @@
       <c r="K3">
         <v>22</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="M3">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -649,14 +678,20 @@
       <c r="K4">
         <v>22</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="37.5">
+      <c r="M4">
+        <v>22</v>
+      </c>
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -690,14 +725,20 @@
       <c r="K5">
         <v>22</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" t="s">
         <v>34</v>
       </c>
-      <c r="M5" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="M5">
+        <v>22</v>
+      </c>
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
@@ -731,39 +772,45 @@
       <c r="K6">
         <v>22</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="M6">
+        <v>22</v>
+      </c>
+      <c r="N6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Goal/GoalMessage.xlsx
+++ b/Assets/Originals/Excels/Goal/GoalMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Goal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C5E156-5D4F-4F99-8F76-A19045462CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECCAD9A-408E-4189-87DF-B0D24109CC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -179,6 +179,24 @@
   </si>
   <si>
     <t>Это не тот предмет</t>
+  </si>
+  <si>
+    <t>messageGerman</t>
+  </si>
+  <si>
+    <t>messageSizeGerman</t>
+  </si>
+  <si>
+    <t>Sammle die Dokumente</t>
+  </si>
+  <si>
+    <t>Sammle die Mysteriösen Gegenstände</t>
+  </si>
+  <si>
+    <t>Wähle den Gegenstand, der zum Dokument passt</t>
+  </si>
+  <si>
+    <t>Das ist nicht der richtige Gegenstand</t>
   </si>
 </sst>
 </file>
@@ -526,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="45.375" style="1" customWidth="1"/>
@@ -543,9 +561,11 @@
     <col min="13" max="13" width="23.625" customWidth="1"/>
     <col min="14" max="14" width="76.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="47.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -591,13 +611,19 @@
       <c r="O1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>1</v>
       </c>
@@ -643,8 +669,14 @@
       <c r="O3">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>2</v>
       </c>
@@ -690,8 +722,14 @@
       <c r="O4">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="37.5">
+      <c r="P4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -737,8 +775,14 @@
       <c r="O5">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="P5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>4</v>
       </c>
@@ -784,33 +828,39 @@
       <c r="O6">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Goal/GoalMessage.xlsx
+++ b/Assets/Originals/Excels/Goal/GoalMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Goal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECCAD9A-408E-4189-87DF-B0D24109CC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16737EC2-997C-4F02-96B7-B503CC41A8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -197,6 +197,24 @@
   </si>
   <si>
     <t>Das ist nicht der richtige Gegenstand</t>
+  </si>
+  <si>
+    <t>messageFrench</t>
+  </si>
+  <si>
+    <t>messageSizeFrench</t>
+  </si>
+  <si>
+    <t>Rassemblez les Documents</t>
+  </si>
+  <si>
+    <t>Rassemblez les Objets mystérieux</t>
+  </si>
+  <si>
+    <t>Choisissez l'objet lié au Document</t>
+  </si>
+  <si>
+    <t>Ce n'est pas le bon objet</t>
   </si>
 </sst>
 </file>
@@ -544,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="45.375" style="1" customWidth="1"/>
@@ -563,9 +581,11 @@
     <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="47.75" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="41.25" customWidth="1"/>
+    <col min="19" max="19" width="23.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -617,13 +637,19 @@
       <c r="Q1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>1</v>
       </c>
@@ -675,8 +701,14 @@
       <c r="Q3">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>2</v>
       </c>
@@ -728,8 +760,14 @@
       <c r="Q4">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="37.5">
+      <c r="R4" t="s">
+        <v>51</v>
+      </c>
+      <c r="S4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -781,8 +819,14 @@
       <c r="Q5">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>4</v>
       </c>
@@ -834,33 +878,39 @@
       <c r="Q6">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:19">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Goal/GoalMessage.xlsx
+++ b/Assets/Originals/Excels/Goal/GoalMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Goal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16737EC2-997C-4F02-96B7-B503CC41A8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB32C63-218B-49C9-A71E-CB1714B60474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -215,6 +215,24 @@
   </si>
   <si>
     <t>Ce n'est pas le bon objet</t>
+  </si>
+  <si>
+    <t>messageTurkish</t>
+  </si>
+  <si>
+    <t>messageSizeTurkish</t>
+  </si>
+  <si>
+    <t>Belgeleri topla</t>
+  </si>
+  <si>
+    <t>Gizemli Eşyaları topla</t>
+  </si>
+  <si>
+    <t>Belgeyle ilgili eşyayı seç</t>
+  </si>
+  <si>
+    <t>Doğru eşya bu değil</t>
   </si>
 </sst>
 </file>
@@ -562,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="45.375" style="1" customWidth="1"/>
@@ -583,9 +601,11 @@
     <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="41.25" customWidth="1"/>
     <col min="19" max="19" width="23.625" customWidth="1"/>
+    <col min="20" max="20" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -643,13 +663,19 @@
       <c r="S1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" t="s">
+        <v>54</v>
+      </c>
+      <c r="U1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:21">
       <c r="A3">
         <v>1</v>
       </c>
@@ -707,8 +733,14 @@
       <c r="S3">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="T3" t="s">
+        <v>56</v>
+      </c>
+      <c r="U3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4">
         <v>2</v>
       </c>
@@ -766,8 +798,14 @@
       <c r="S4">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" ht="37.5">
+      <c r="T4" t="s">
+        <v>57</v>
+      </c>
+      <c r="U4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -825,8 +863,14 @@
       <c r="S5">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5" t="s">
+        <v>58</v>
+      </c>
+      <c r="U5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>4</v>
       </c>
@@ -884,33 +928,39 @@
       <c r="S6">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6" t="s">
+        <v>59</v>
+      </c>
+      <c r="U6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:21">
       <c r="A8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:21">
       <c r="A9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:21">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:21">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:21">
       <c r="A12">
         <v>10</v>
       </c>
